--- a/orbitalx-seo-audit.xlsx
+++ b/orbitalx-seo-audit.xlsx
@@ -8,15 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Wins" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duplicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta Drafts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords (Semrush US)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword Targets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pages (Semrush US)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Inventory" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duplicates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta Drafts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Quick Wins'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page Inventory'!$A$1:$N$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Duplicates'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Meta Drafts'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keywords (Semrush US)'!$A$1:$K$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Keyword Targets'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pages (Semrush US)'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Page Inventory'!$A$1:$P$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Duplicates'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Meta Drafts'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -485,17 +491,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Write unique meta descriptions for 83 articles + 13 taxonomy pages; set SEO Pro fallback to excerpt</t>
+          <t>Noindex app.orbitalx.com (X-Robots-Tag via Netlify _headers); retitle from "Smartlead"</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1-2 days</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -505,7 +511,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
@@ -515,27 +521,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>301 the 3 exact duplicates and merge 4 near-duplicates; remove retired URLs from sitemap</t>
+          <t>Push the 9 striking-distance / high-value keywords (see Keyword Targets tab)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Dev/Content</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -545,7 +551,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Add 1-3 contextual service-page links in each of the 52 long-form guides + service CTA block in article template</t>
+          <t>Fix cannibalization: retitle homepage, /resources/account-based-marketing-services, /resources/demand-gen-agency; category intro → /services/demand-generation</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -555,7 +561,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1-2 days</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +571,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.4, 1.5</t>
         </is>
       </c>
     </row>
@@ -575,7 +581,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fix ABM / demand gen cannibalization: retitle homepage, /resources/account-based-marketing-services, /resources/demand-gen-agency</t>
+          <t>Add 1-3 in-text service-page links in each of the 52 long-form guides (start with posts that already rank)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -585,7 +591,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>1-2 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +601,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.1, 1.5</t>
         </is>
       </c>
     </row>
@@ -605,7 +611,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Name, intro copy and meta for 13 category/type pages; noindex or merge categories with &lt;3 posts</t>
+          <t>Unique meta descriptions for 83 articles + 13 taxonomy pages; SEO Pro fallback to excerpt</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -615,7 +621,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.5 day</t>
+          <t>1-2 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -625,7 +631,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -635,17 +641,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting + BreadcrumbList + Person schema and visible bylines; fix Organization schema</t>
+          <t>301 the 3 exact duplicates; merge the 4 near-duplicates</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>Dev/Content</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0.5 day</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -655,7 +661,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2.2, 2.3</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
@@ -665,7 +671,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Make /resources pagination crawlable (real page 2+, self-canonical)</t>
+          <t>robots.txt sitemap host; www. internal links; sameAs/GBP URL → non-www; footer link to /faqs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -675,17 +681,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0.5 day</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.7, 2.10, 2.11</t>
         </is>
       </c>
     </row>
@@ -695,7 +701,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>robots.txt sitemap host; replace www. internal links; footer link to /faqs; paragraph H2s → &lt;p&gt;</t>
+          <t>BlogPosting + BreadcrumbList + Person schema; fix Organization; crawlable /resources pagination</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -705,17 +711,47 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Low-Med</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2.7, 2.10, 2.11</t>
+          <t>1.2, 2.2, 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Name, intro and meta for 13 category/type pages</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0.5 day</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2.4</t>
         </is>
       </c>
     </row>
@@ -731,7 +767,5907 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N153"/>
+  <dimension ref="A1:K97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Brand?</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pos</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CPC $</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SERP features</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>programmatic advertising b2b</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>larger market formula</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>/resources/the-larger-market-formula-your-next-b2b-software-success-strategy</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Image pack, Reviews, Video, Image, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ai marketing agent qualify intent book meetings</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>/resources/ai-lead-generation</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>demand gen software</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>140</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, Video Carousel, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>enterprise abm teams results turtl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>informational, navigational</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Reviews, Video, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>b2b accounts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>140</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Reviews, Video, Image, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>demand gen vs performance max</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>140</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>yieldify</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>110</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>/resources/behind-the-numbers-how-yieldify-made-every-rep-count</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>yieldify</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>110</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>/resources/behind-the-numbers-how-yieldify-made-every-rep-count</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>how are other marketing teams solving complex rendering performance requirements</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-optimization</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>demand gen company</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>480</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>/blog-categories/demand-generation</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>deltay.xyz target audience b2b smes</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>/resources</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Reviews, Video, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>demand gen vs pmax</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>account based selling strategy software</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-software</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Related searches, Discussions and forums, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>b2b go-to-market optimization partners</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/resources/b2b-go-to-market-strategy</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Video, Video Carousel, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>personalization in account based marketing means</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-personalization</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>account based marketing content strategy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>140</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>b2b software companies disjointed sales marketing systems revenue impact</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/resources/lead-generation-chatbot</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nexxi b2b go-to-market enablement ai-native teams</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/resources/b2b-go-to-market-strategy</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Reviews, Video, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>account based advertising software market</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>70</v>
+      </c>
+      <c r="F23" t="n">
+        <v>32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-software</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>nexxi b2b go-to-market enablement alternatives</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>34</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/resources/b2b-go-to-market-strategy</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>demand gen vs. lead gen</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>38</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>40</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Image pack, Reviews, Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>demand generation program</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>260</v>
+      </c>
+      <c r="F26" t="n">
+        <v>34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/resources/demand-generation-programs</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>38</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>210</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>top services for scaling account-based marketing</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>39</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>account-based outreach software</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>41</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>lead scoring model for seo growth intent</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>45</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>880</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>/resources/b2b-marketing</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abm personalization tools</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>46</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>70</v>
+      </c>
+      <c r="F31" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-personalization</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>google ads demand gen vs performance max optimization</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>47</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Video Carousel, People also ask, Related searches, Discussions and forums, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>top abm software providers</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>47</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>40</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Ads bottom, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>best account-based marketing platform for demand generation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>49</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>40</v>
+      </c>
+      <c r="F34" t="n">
+        <v>26</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>top abm software providers</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>40</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Ads bottom, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>account based marketing platforms with intent signals</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>51</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>abm personalization tools</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>52</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>70</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>account based marketing for enterprise</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>52</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>40</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/resources/enterprise-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>top abm tools programmatic account-based advertising</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>52</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>40</v>
+      </c>
+      <c r="F39" t="n">
+        <v>33</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>54</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>210</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>abm tools with contact-level intent</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>57</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>70</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Reviews, Video, Ads bottom, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>account based everything b2b marketing</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>58</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Video Carousel, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>account based everything b2b marketing</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>59</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F43" t="n">
+        <v>35</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Video Carousel, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>demand gen firm</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>59</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>110</v>
+      </c>
+      <c r="F44" t="n">
+        <v>38</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-agency</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>demand gen firm</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>60</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>110</v>
+      </c>
+      <c r="F45" t="n">
+        <v>38</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-agency</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>demand generation recruiters</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>61</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>40</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-agency</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Reviews, Video, Ads top, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>account-based marketing tool</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>63</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" t="n">
+        <v>41</v>
+      </c>
+      <c r="G47" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>account-based marketing solutions</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>64</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>40</v>
+      </c>
+      <c r="F48" t="n">
+        <v>37</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>b2b go-to-market partners for logistics brands</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>64</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>40</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>/resources/b2b-go-to-market-strategy</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gtm engineering signal-driven flywheels definition</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>64</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>110</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>/resources/the-4-step-flywheel-effect-a-proven-evergreen-framework-for-gtm-success</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>account based marketing planning services</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>69</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>170</v>
+      </c>
+      <c r="F51" t="n">
+        <v>35</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>difference between demand gen and lead gen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>69</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>/resources/lead-generation-vs-demand-generation-understanding-the-differences-and-benefits</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>top abm tools programmatic account-based advertising</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>69</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>40</v>
+      </c>
+      <c r="F53" t="n">
+        <v>33</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>account based marketing platform</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>73</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>170</v>
+      </c>
+      <c r="F54" t="n">
+        <v>57</v>
+      </c>
+      <c r="G54" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>account based marketing planning services</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>74</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>170</v>
+      </c>
+      <c r="F55" t="n">
+        <v>35</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>account based marketing vendors</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>76</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>320</v>
+      </c>
+      <c r="F56" t="n">
+        <v>47</v>
+      </c>
+      <c r="G56" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>abm personalization tools</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>78</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F57" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-personalization</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>account based marketing solutions</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>79</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>210</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>abx campaign</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>80</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>110</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13</v>
+      </c>
+      <c r="G59" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>/services/abm</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, Video Carousel, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>abx platforms</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>80</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-software</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>leading account-based marketing consulting options for large software firms</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>85</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>40</v>
+      </c>
+      <c r="F61" t="n">
+        <v>11</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>commercial, informational</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>difference between demand gen and lead gen</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Non-brand</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>92</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>50</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>/resources/lead-generation-vs-demand-generation-understanding-the-differences-and-benefits</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>170</v>
+      </c>
+      <c r="F63" t="n">
+        <v>50</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>136</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>x orbital</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>50</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>informational, navigational</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>170</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>/team</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>170</v>
+      </c>
+      <c r="F66" t="n">
+        <v>50</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>170</v>
+      </c>
+      <c r="F67" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>/contact</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>withorbital</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>14</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>30</v>
+      </c>
+      <c r="F68" t="n">
+        <v>27</v>
+      </c>
+      <c r="G68" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>/resources</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>x orbital</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" t="n">
+        <v>36</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>/team</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>informational, navigational</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>billionx</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>19</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>110</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>withorbital</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>19</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>11-20 (striking)</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>30</v>
+      </c>
+      <c r="F71" t="n">
+        <v>27</v>
+      </c>
+      <c r="G71" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>demandx</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>26</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>/blog-categories/demand-generation</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>orbit-x</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>46</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" t="n">
+        <v>24</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Popular products, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>orbital management</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>47</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>40</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>47</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>21-50</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>170</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>/legal/terms-of-service</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>asteroidx</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>51</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>110</v>
+      </c>
+      <c r="F76" t="n">
+        <v>30</v>
+      </c>
+      <c r="G76" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>orbit x</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>51</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>90</v>
+      </c>
+      <c r="F77" t="n">
+        <v>19</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>orbitx</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>52</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F78" t="n">
+        <v>51</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Image pack, Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>orbital llc</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>55</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" t="n">
+        <v>33</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>61</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>170</v>
+      </c>
+      <c r="F80" t="n">
+        <v>50</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>/services</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>orbital tech</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>62</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>110</v>
+      </c>
+      <c r="F81" t="n">
+        <v>39</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>orbital inc.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>68</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>110</v>
+      </c>
+      <c r="F82" t="n">
+        <v>51</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>68</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>170</v>
+      </c>
+      <c r="F83" t="n">
+        <v>50</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>/services/ai-agents</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>orbital technologies</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>69</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>40</v>
+      </c>
+      <c r="F84" t="n">
+        <v>19</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>navigational</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Local pack, Sitelinks, Video, People also ask, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>demandx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>70</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>50</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Image pack, Sitelinks, Reviews, Video, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>orbital company</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>70</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>170</v>
+      </c>
+      <c r="F86" t="n">
+        <v>60</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Local pack, Sitelinks, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>orbital software</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>75</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>90</v>
+      </c>
+      <c r="F87" t="n">
+        <v>46</v>
+      </c>
+      <c r="G87" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Sitelinks, Reviews, Video, People also ask, Related searches, AI overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>76</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>170</v>
+      </c>
+      <c r="F88" t="n">
+        <v>50</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>/platform</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>77</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>170</v>
+      </c>
+      <c r="F89" t="n">
+        <v>50</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>/platform</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>80</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>170</v>
+      </c>
+      <c r="F90" t="n">
+        <v>50</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>/how-it-works</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>82</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>170</v>
+      </c>
+      <c r="F91" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>/be-a-guest</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>84</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>170</v>
+      </c>
+      <c r="F92" t="n">
+        <v>50</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>86</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>170</v>
+      </c>
+      <c r="F93" t="n">
+        <v>50</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>/resources/how-the-smartest-hire-grew-pipeline-at-private-equity-backed-cylindo-without-a-marketing-team</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>88</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>170</v>
+      </c>
+      <c r="F94" t="n">
+        <v>50</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>90</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>170</v>
+      </c>
+      <c r="F95" t="n">
+        <v>50</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>/services/paid</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>92</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>170</v>
+      </c>
+      <c r="F96" t="n">
+        <v>50</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>/services/owned</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Brand/look-alike</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>95</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>51-100</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>170</v>
+      </c>
+      <c r="F97" t="n">
+        <v>50</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>/legal/privacy-policy</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Knowledge panel, Image pack, Sitelinks, Reviews, Video, Related searches</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K97"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CPC $</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Current pos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>demand gen vs performance max</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>140</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Comparison table up top, "when to use which", FAQ; retitle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>demand gen software</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>140</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ranked tool list + comparison table; keyword-first title; link to /services/demand-generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>210</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-tools</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Add job-change/hiring-signals section; remove overlap from demand-gen-software</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ai marketing agent qualify intent book meetings</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>/resources/ai-lead-generation</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Add matching H2; link to /services/ai-agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b2b accounts</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>140</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Short definition section (low priority)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>demand gen company</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>480</v>
+      </c>
+      <c r="C7" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>/blog-categories/demand-generation</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Retarget to /services/demand-generation; category intro links to service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>demand generation program</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>260</v>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>/resources/demand-generation-programs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unique meta, template/download, category link</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>account based marketing vendors</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>320</v>
+      </c>
+      <c r="C9" t="n">
+        <v>47</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>76</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>"ABM vendors / platforms" in H2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>account based marketing platform</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>170</v>
+      </c>
+      <c r="C10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D10" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Add best-ABM-platforms comparison rows</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic %</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Keywords</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic change</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Top keyword</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Answer engines</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LLM prompts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90.66</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>136</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-tools</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>performance marketing job category signals</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>/resources/the-larger-market-formula-your-next-b2b-software-success-strategy</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>larger market formula</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>/team</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>/resources</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>withorbital</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>/how-it-works</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>/legal/privacy-policy</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>/resources/demand-generation-programs</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>/blog-categories/demand-generation</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-vs-performance-max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>demand gen vs performance max</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>/resources/b2b-marketing-strategies</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>/resources/performance-marketing-optimization</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>/legal/terms-of-service</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>/resources/b2b-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>b2b accounts</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>google-ai</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>/resources/lead-generation-chatbot</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-funnel</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>search-gpt</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>/contact</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>orbital x</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>/resources/ai-lead-generation</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ai marketing agent qualify intent book meetings</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-software</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>/resources/enterprise-account-based-marketing</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>/services/abm</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-software</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>demand gen software</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>/services/paid</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-tools</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>19</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>enterprise abm teams results turtl</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>/resources/the-4-step-flywheel-effect-a-proven-evergreen-framework-for-gtm-success</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>/be-a-guest</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>/resources/how-the-smartest-hire-grew-pipeline-at-private-equity-backed-cylindo-without-a-marketing-team</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>/resources/b2b-go-to-market-strategy</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>/resources/demand-gen-agency</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>/resources/behind-the-numbers-how-yieldify-made-every-rep-count</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yieldify</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>/resources/lead-generation-vs-demand-generation-understanding-the-differences-and-benefits</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://app.orbitalx.com/</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>/services/ai-agents</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>/services/owned</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>/resources/b2b-marketing</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>/services</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>/resources/account-based-marketing-personalization</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>/platform</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H40"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -821,6 +6757,16 @@
           <t>Issues</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Semrush keywords (US)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Best position</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -875,6 +6821,12 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -929,6 +6881,12 @@
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -987,6 +6945,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1045,6 +7006,9 @@
           <t>Generic meta; ≤1 internal link pointing here; Slug used as title/H1</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1103,6 +7067,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1161,6 +7128,9 @@
           <t>Generic meta; ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1219,6 +7189,9 @@
           <t>Generic meta; ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1277,6 +7250,12 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1335,6 +7314,9 @@
           <t>Generic meta; ≤1 internal link pointing here; Slug used as title/H1</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1393,6 +7375,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1451,6 +7436,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1505,6 +7493,9 @@
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1559,6 +7550,9 @@
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1613,6 +7607,12 @@
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1671,6 +7671,9 @@
           <t>≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1725,6 +7728,12 @@
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1779,6 +7788,12 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1833,6 +7848,12 @@
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1887,6 +7908,12 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1945,6 +7972,9 @@
           <t>Generic meta; ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2003,6 +8033,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2061,6 +8094,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2119,6 +8155,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2173,6 +8212,12 @@
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2231,6 +8276,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2289,6 +8337,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2347,6 +8398,9 @@
           <t>Generic meta; Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2405,6 +8459,9 @@
           <t>Generic meta; ≤1 internal link pointing here; Long title</t>
         </is>
       </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2463,6 +8520,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2521,6 +8581,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2579,6 +8642,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2637,6 +8706,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2695,6 +8767,12 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2753,6 +8831,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2811,6 +8892,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O36" t="n">
+        <v>16</v>
+      </c>
+      <c r="P36" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2869,6 +8956,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2927,6 +9017,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2985,6 +9081,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3043,6 +9145,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3101,6 +9206,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3159,6 +9267,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3217,6 +9328,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3275,6 +9392,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3333,6 +9453,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3391,6 +9517,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3449,6 +9578,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3507,6 +9639,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3565,6 +9700,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3623,6 +9761,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3681,6 +9822,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3739,6 +9883,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3797,6 +9944,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3855,6 +10005,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3913,6 +10066,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3971,6 +10127,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4029,6 +10188,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4087,6 +10249,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4145,6 +10310,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4199,6 +10367,12 @@
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4257,6 +10431,9 @@
           <t>Generic meta; Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4315,6 +10492,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4369,6 +10549,9 @@
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4427,6 +10610,9 @@
           <t>Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4485,6 +10671,12 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O65" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4543,6 +10735,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4601,6 +10796,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O67" t="n">
+        <v>3</v>
+      </c>
+      <c r="P67" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4659,6 +10860,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4717,6 +10921,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O69" t="n">
+        <v>4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4775,6 +10985,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4829,6 +11045,9 @@
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4887,6 +11106,9 @@
           <t>Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4945,6 +11167,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5003,6 +11228,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5061,6 +11289,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5119,6 +11350,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5177,6 +11414,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5235,6 +11475,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5293,6 +11536,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5351,6 +11597,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5405,6 +11654,9 @@
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5463,6 +11715,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5521,6 +11776,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5579,6 +11837,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5637,6 +11898,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5695,6 +11959,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5749,6 +12016,9 @@
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5807,6 +12077,9 @@
           <t>Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5865,6 +12138,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title</t>
         </is>
       </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5919,6 +12195,9 @@
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5977,6 +12256,9 @@
           <t>Thin (&lt;600 words)</t>
         </is>
       </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6035,6 +12317,12 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6093,6 +12381,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6151,6 +12442,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6205,6 +12499,9 @@
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6263,6 +12560,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6321,6 +12621,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title</t>
         </is>
       </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6379,6 +12682,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title</t>
         </is>
       </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6437,6 +12743,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6491,6 +12800,9 @@
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6549,6 +12861,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6607,6 +12922,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6665,6 +12986,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6723,6 +13047,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6781,6 +13108,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6839,6 +13169,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6897,6 +13230,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6955,6 +13291,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7013,6 +13352,12 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7071,6 +13416,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7129,6 +13477,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7187,6 +13538,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7245,6 +13599,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7303,6 +13660,9 @@
           <t>Generic meta; Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7361,6 +13721,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7419,6 +13782,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7477,6 +13843,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7535,6 +13904,9 @@
           <t>Thin (&lt;600 words); ≤1 internal link pointing here</t>
         </is>
       </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7593,6 +13965,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7651,6 +14026,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7709,6 +14090,12 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7767,6 +14154,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7825,6 +14215,9 @@
           <t>Generic meta</t>
         </is>
       </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7883,6 +14276,12 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7941,6 +14340,9 @@
           <t>Generic meta; Thin (&lt;600 words)</t>
         </is>
       </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7999,6 +14401,9 @@
           <t>Generic meta; Thin (&lt;600 words)</t>
         </is>
       </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8057,6 +14462,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8115,6 +14523,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8173,6 +14584,12 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8231,6 +14648,9 @@
           <t>Generic meta; Thin (&lt;600 words)</t>
         </is>
       </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8289,6 +14709,9 @@
           <t>Generic meta; Thin (&lt;600 words)</t>
         </is>
       </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8347,6 +14770,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8405,6 +14831,9 @@
           <t>Generic meta; Thin (&lt;600 words); ≤1 internal link pointing here; Long title; Duplicate → 301/merge</t>
         </is>
       </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8463,6 +14892,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8521,6 +14953,9 @@
           <t>Generic meta; Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8579,6 +15014,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8637,6 +15075,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8695,6 +15136,9 @@
           <t>Generic meta; Thin (&lt;600 words); Long title</t>
         </is>
       </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8753,6 +15197,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8811,6 +15258,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8865,6 +15315,9 @@
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8923,6 +15376,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8981,6 +15437,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9039,6 +15498,9 @@
           <t>Generic meta; Long title</t>
         </is>
       </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9093,6 +15555,9 @@
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9147,6 +15612,12 @@
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9205,6 +15676,12 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9259,6 +15736,12 @@
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9317,6 +15800,9 @@
           <t>Long title</t>
         </is>
       </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9371,6 +15857,9 @@
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9425,6 +15914,12 @@
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9479,6 +15974,12 @@
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9533,14 +16034,20 @@
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" t="n">
+        <v>2</v>
+      </c>
+      <c r="P153" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N153"/>
+  <autoFilter ref="A1:P153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9781,7 +16288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/orbitalx-seo-audit.xlsx
+++ b/orbitalx-seo-audit.xlsx
@@ -596,13 +596,13 @@
     <t xml:space="preserve">Service pages duplicate the homepage</t>
   </si>
   <si>
-    <t xml:space="preserve">46–63% of each main service page's text is copied from the homepage.</t>
+    <t xml:space="preserve">46–63% of each main service page's text is copied from the homepage. Identical sections: proof bar, 'One system that runs your entire pipeline engine', 'How it works', 'What it costs to build this yourself', testimonials, 'See how your target accounts see you'. Partly copied: 'Real results' and FAQs.</t>
   </si>
   <si>
     <t xml:space="preserve">Thin / duplicate signals</t>
   </si>
   <si>
-    <t xml:space="preserve">Rewrite the 'broken', 'how it works' and FAQ blocks per service.</t>
+    <t xml:space="preserve">Rewrite 'One system…', 'How it works' and 'What it costs…' per service; make FAQs and results service-specific. Keep proof bar and testimonials.</t>
   </si>
   <si>
     <t xml:space="preserve">G16</t>
@@ -5600,11 +5600,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4013204"/>
-        <c:axId val="72198085"/>
+        <c:axId val="85169958"/>
+        <c:axId val="36620475"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4013204"/>
+        <c:axId val="85169958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5636,7 +5636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72198085"/>
+        <c:crossAx val="36620475"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5644,7 +5644,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72198085"/>
+        <c:axId val="36620475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5686,7 +5686,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4013204"/>
+        <c:crossAx val="85169958"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6390,11 +6390,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64017951"/>
-        <c:axId val="38289114"/>
+        <c:axId val="51679653"/>
+        <c:axId val="30840619"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="64017951"/>
+        <c:axId val="51679653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6426,7 +6426,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38289114"/>
+        <c:crossAx val="30840619"/>
         <c:crosses val="max"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6434,7 +6434,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38289114"/>
+        <c:axId val="30840619"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -6476,7 +6476,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64017951"/>
+        <c:crossAx val="51679653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21766,7 +21766,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
         <v>172</v>
       </c>
@@ -28216,7 +28216,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{962C4853-8B60-4840-A255-EBB64DA4FE72}</x14:id>
+          <x14:id>{D197C9BE-FAAE-4950-A832-B6ECE22FACCC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -28234,7 +28234,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{962C4853-8B60-4840-A255-EBB64DA4FE72}">
+          <x14:cfRule type="dataBar" id="{D197C9BE-FAAE-4950-A832-B6ECE22FACCC}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
